--- a/questionnaire_templates/036_essential_oil_and_wellness_quiz--questionnaire_templates.xlsx
+++ b/questionnaire_templates/036_essential_oil_and_wellness_quiz--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1018,17 +1018,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>oil_benefits_choices</t>
+          <t>oil_uses_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mood</t>
+          <t>aroma</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mood</t>
+          <t>Aroma</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>aroma</t>
+          <t>diffuse</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Diffuse</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>diffuse</t>
+          <t>topical</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Diffuse</t>
+          <t>Topical</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>topical</t>
+          <t>inhalation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Topical</t>
+          <t>Inhalation</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>inhalation</t>
+          <t>sublingual</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inhalation</t>
+          <t>Sublingual</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sublingual</t>
+          <t>oral</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sublingual</t>
+          <t>Oral</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>oral</t>
+          <t>bath</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oral</t>
+          <t>Bath</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bath</t>
+          <t>skincare</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Skincare</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>skincare</t>
+          <t>haircare</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Skincare</t>
+          <t>Haircare</t>
         </is>
       </c>
     </row>
@@ -1176,29 +1176,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>haircare</t>
+          <t>massage</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Haircare</t>
+          <t>Massage</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>oil_uses_choices</t>
+          <t>oil_characteristics_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>massage</t>
+          <t>potency</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Massage</t>
+          <t>Potency</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>potency</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Potency</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>purity</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Purity</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>purity</t>
+          <t>freshness</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Purity</t>
+          <t>Freshness</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>freshness</t>
+          <t>expiration</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Freshness</t>
+          <t>Expiration</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>expiration</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Expiration</t>
+          <t>Label</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>brand</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Brand</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>brand</t>
+          <t>concentration</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Concentration</t>
         </is>
       </c>
     </row>
@@ -1329,19 +1329,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>shelf</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Concentration</t>
+          <t>Shelf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>oil_characteristics_choices</t>
+          <t>customer_perception_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1358,17 +1358,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>oil_characteristics_choices</t>
+          <t>customer_perception_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>shelf</t>
+          <t>brand</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Shelf</t>
+          <t>Brand</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>brand</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>expiration</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Expiration</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>concentration</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Concentration</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>expiration</t>
+          <t>shelf</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Expiration</t>
+          <t>Shelf</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>potency</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Concentration</t>
+          <t>Potency</t>
         </is>
       </c>
     </row>
@@ -1482,61 +1482,10 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>purity</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>customer_perception_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>shelf</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Shelf</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>customer_perception_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>potency</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Potency</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>customer_perception_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>purity</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
         <is>
           <t>Purity</t>
         </is>
